--- a/Results/Consensus_more_than_2/MC/MC_TCGA_RNAseq-CNV-Methylation-miRNA-SNPs_eval_on_transNEO_clusterings.xlsx
+++ b/Results/Consensus_more_than_2/MC/MC_TCGA_RNAseq-CNV-Methylation-miRNA-SNPs_eval_on_transNEO_clusterings.xlsx
@@ -4070,7 +4070,7 @@
         <v>234</v>
       </c>
       <c r="B230" t="s">
-        <v>3</v>
+        <v>22</v>
       </c>
     </row>
     <row r="231">
@@ -5222,7 +5222,7 @@
         <v>378</v>
       </c>
       <c r="B374" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="375">
@@ -5566,7 +5566,7 @@
         <v>421</v>
       </c>
       <c r="B417" t="s">
-        <v>3</v>
+        <v>22</v>
       </c>
     </row>
     <row r="418">
@@ -5950,7 +5950,7 @@
         <v>469</v>
       </c>
       <c r="B465" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="466">
